--- a/TestAutomation/TestData/Credentials.xlsx
+++ b/TestAutomation/TestData/Credentials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\TestAutomation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\Final_Dissertation\TestAutomation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21812C93-A662-4993-8505-A5D4FA82A43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E059E2-C63E-4260-B425-DB57B6DB509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7656B5F3-7B38-46D2-9665-1CE8647B30BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Scenario</t>
   </si>
@@ -71,13 +71,25 @@
     <t>Passss</t>
   </si>
   <si>
-    <t>invalid</t>
-  </si>
-  <si>
     <t>Successfully</t>
   </si>
   <si>
     <t>expected_result</t>
+  </si>
+  <si>
+    <t>Your username is invalid!</t>
+  </si>
+  <si>
+    <t>Your password is invalid!</t>
+  </si>
+  <si>
+    <t>Scenario4</t>
+  </si>
+  <si>
+    <t>studen</t>
+  </si>
+  <si>
+    <t>Password122</t>
   </si>
 </sst>
 </file>
@@ -449,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE00BEC-F5C2-4A8F-BE69-7E270B9EA6BF}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -467,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -481,7 +493,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -495,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -509,7 +521,21 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/TestAutomation/TestData/Credentials.xlsx
+++ b/TestAutomation/TestData/Credentials.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\Final_Dissertation\TestAutomation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E059E2-C63E-4260-B425-DB57B6DB509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210DAADD-31F2-44AF-BFB5-FD103C8303CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7656B5F3-7B38-46D2-9665-1CE8647B30BE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Scenario</t>
   </si>
@@ -90,16 +90,36 @@
   </si>
   <si>
     <t>Password122</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://practicetestautomation.com/practice-test-login</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -122,13 +142,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -461,84 +484,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE00BEC-F5C2-4A8F-BE69-7E270B9EA6BF}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{83E69E42-3E42-4DC7-B7E8-FC1FF5B8943F}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{8954AAAE-ACC5-4618-A97E-F2E1EEB5F302}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{FEB5805A-F748-4188-9BDA-DFB21BA04154}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{ECF74A3F-9AFC-4540-B1AF-8F271B683FCC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestAutomation/TestData/Credentials.xlsx
+++ b/TestAutomation/TestData/Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\Final_Dissertation\TestAutomation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210DAADD-31F2-44AF-BFB5-FD103C8303CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C243ED2-A0AF-4E18-9636-EAC0A16552E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7656B5F3-7B38-46D2-9665-1CE8647B30BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Scenario</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>https://practicetestautomation.com/practice-test-login</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE00BEC-F5C2-4A8F-BE69-7E270B9EA6BF}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -574,6 +577,11 @@
       </c>
       <c r="E5" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/TestAutomation/TestData/Credentials.xlsx
+++ b/TestAutomation/TestData/Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\Final_Dissertation\TestAutomation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C243ED2-A0AF-4E18-9636-EAC0A16552E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E531ED8C-4C96-489A-8350-3219CA2A232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7656B5F3-7B38-46D2-9665-1CE8647B30BE}"/>
   </bookViews>
@@ -92,20 +92,20 @@
     <t>Password122</t>
   </si>
   <si>
-    <t>URL</t>
-  </si>
-  <si>
     <t>https://practicetestautomation.com/practice-test-login</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>url</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,13 +127,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -149,9 +163,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -495,19 +510,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -516,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -533,7 +548,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -550,7 +565,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -567,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -581,7 +596,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/TestAutomation/TestData/Credentials.xlsx
+++ b/TestAutomation/TestData/Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padma\Projects\Final_Dissertation\TestAutomation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E531ED8C-4C96-489A-8350-3219CA2A232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7422D0-F3C2-40F3-B4E7-68F4A884E950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7656B5F3-7B38-46D2-9665-1CE8647B30BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Scenario</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>https://practicetestautomation.com/practice-test-login</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>url</t>
@@ -105,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +128,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -165,8 +169,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -502,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE00BEC-F5C2-4A8F-BE69-7E270B9EA6BF}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -510,19 +514,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -530,7 +534,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
@@ -547,7 +551,7 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
@@ -564,7 +568,7 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
@@ -581,7 +585,7 @@
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -592,11 +596,6 @@
       </c>
       <c r="E5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
